--- a/data/trans_bre/IP16A01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,87; 53,71</t>
+          <t>4,76; 55,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-38,92; 17,25</t>
+          <t>-39,58; 18,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 10,63</t>
+          <t>-46,81; 7,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,24 +685,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,98; 156,58</t>
+          <t>8,54; 184,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,6; 37,27</t>
+          <t>-56,0; 41,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-66,31; 22,1</t>
+          <t>-67,88; 15,35</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 21,53</t>
+          <t>-24,03; 22,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 44,2</t>
+          <t>0,95; 46,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 39,95</t>
+          <t>-18,25; 47,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,24 +785,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 45,11</t>
+          <t>-33,87; 47,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 121,92</t>
+          <t>1,82; 132,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 93,22</t>
+          <t>-30,68; 110,12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 13,39</t>
+          <t>-33,71; 14,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,78; 34,25</t>
+          <t>-43,96; 42,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 22,95</t>
+          <t>-23,76; 22,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 18,42</t>
+          <t>-39,58; 19,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-57,24; 106,6</t>
+          <t>-55,59; 119,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 38,65</t>
+          <t>-28,37; 38,61</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 39,86</t>
+          <t>-13,41; 39,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 17,63</t>
+          <t>-27,59; 17,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,47; 17,66</t>
+          <t>-52,64; 20,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 88,16</t>
+          <t>-15,86; 95,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,98; 34,76</t>
+          <t>-39,97; 37,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,64; 32,44</t>
+          <t>-63,18; 45,05</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 31,02</t>
+          <t>-17,69; 32,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,97; 53,69</t>
+          <t>-22,23; 55,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 63,7</t>
+          <t>-7,53; 60,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,24 +1085,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,23; 53,53</t>
+          <t>-20,79; 53,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-22,91; 136,97</t>
+          <t>-21,94; 159,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 280,49</t>
+          <t>-10,31; 343,39</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 30,72</t>
+          <t>-33,42; 28,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 54,6</t>
+          <t>-22,76; 55,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 15,93</t>
+          <t>-49,06; 16,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,24 +1185,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,35; 69,8</t>
+          <t>-50,29; 61,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,21; 487,55</t>
+          <t>-38,9; 448,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,73; 25,91</t>
+          <t>-60,85; 23,0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 26,45</t>
+          <t>-17,02; 27,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 21,27</t>
+          <t>-37,74; 20,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 20,19</t>
+          <t>-22,37; 20,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 61,9</t>
+          <t>-25,84; 60,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-44,4; 35,85</t>
+          <t>-45,21; 34,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-37,7; 48,22</t>
+          <t>-34,8; 48,89</t>
         </is>
       </c>
     </row>
@@ -1365,17 +1365,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 21,12</t>
+          <t>-25,49; 21,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 33,55</t>
+          <t>-10,59; 37,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 38,03</t>
+          <t>-30,21; 40,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1385,17 +1385,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,3; 49,77</t>
+          <t>-39,15; 54,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 107,67</t>
+          <t>-17,61; 127,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,74; 91,28</t>
+          <t>-43,87; 107,17</t>
         </is>
       </c>
     </row>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 14,36</t>
+          <t>-3,93; 12,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 17,0</t>
+          <t>-4,45; 15,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 18,19</t>
+          <t>-12,3; 18,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 25,25</t>
+          <t>-6,04; 22,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 33,29</t>
+          <t>-7,43; 30,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 34,17</t>
+          <t>-20,25; 33,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Provincia-trans_bre.xlsx
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 55,57</t>
+          <t>5,62; 52,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,58; 18,83</t>
+          <t>-39,72; 14,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-46,81; 7,51</t>
+          <t>-44,72; 6,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,54; 184,55</t>
+          <t>9,53; 149,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-56,0; 41,39</t>
+          <t>-57,54; 34,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-67,88; 15,35</t>
+          <t>-69,36; 13,02</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 22,06</t>
+          <t>-22,13; 22,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 46,1</t>
+          <t>-0,37; 44,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 47,02</t>
+          <t>-19,6; 42,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,87; 47,71</t>
+          <t>-33,0; 48,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 132,35</t>
+          <t>0,31; 128,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,68; 110,12</t>
+          <t>-33,28; 106,81</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-33,71; 14,41</t>
+          <t>-33,59; 13,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,96; 42,13</t>
+          <t>-44,35; 30,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 22,68</t>
+          <t>-22,63; 24,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,58; 19,36</t>
+          <t>-39,53; 19,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 119,55</t>
+          <t>-59,04; 86,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 38,61</t>
+          <t>-27,52; 41,9</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 39,98</t>
+          <t>-9,67; 40,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 17,09</t>
+          <t>-27,38; 18,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,64; 20,02</t>
+          <t>-55,79; 19,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 95,6</t>
+          <t>-11,54; 92,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,97; 37,69</t>
+          <t>-40,4; 38,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,18; 45,05</t>
+          <t>-65,6; 35,64</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 32,37</t>
+          <t>-20,39; 29,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 55,38</t>
+          <t>-21,51; 56,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 60,18</t>
+          <t>-10,2; 63,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 53,43</t>
+          <t>-23,11; 49,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 159,28</t>
+          <t>-19,94; 198,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 343,39</t>
+          <t>-15,72; 303,74</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 28,22</t>
+          <t>-28,94; 32,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 55,36</t>
+          <t>-20,66; 55,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,06; 16,56</t>
+          <t>-49,47; 15,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,29; 61,69</t>
+          <t>-45,27; 83,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,9; 448,13</t>
+          <t>-36,29; 478,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,85; 23,0</t>
+          <t>-58,18; 23,21</t>
         </is>
       </c>
     </row>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 27,47</t>
+          <t>-18,68; 24,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-37,74; 20,97</t>
+          <t>-33,23; 23,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 20,45</t>
+          <t>-25,13; 21,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,84; 60,04</t>
+          <t>-26,86; 59,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-45,21; 34,58</t>
+          <t>-38,89; 41,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-34,8; 48,89</t>
+          <t>-38,57; 50,12</t>
         </is>
       </c>
     </row>
@@ -1365,17 +1365,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,49; 21,9</t>
+          <t>-24,67; 23,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 37,38</t>
+          <t>-10,37; 34,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 40,36</t>
+          <t>-32,2; 38,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1385,17 +1385,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,15; 54,73</t>
+          <t>-39,16; 56,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 127,71</t>
+          <t>-20,69; 103,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,87; 107,17</t>
+          <t>-44,02; 96,69</t>
         </is>
       </c>
     </row>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 12,75</t>
+          <t>-4,01; 14,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 15,19</t>
+          <t>-3,74; 16,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 18,16</t>
+          <t>-12,88; 17,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 22,05</t>
+          <t>-5,81; 24,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 30,38</t>
+          <t>-6,11; 33,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 33,75</t>
+          <t>-21,41; 34,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-17,7</t>
+          <t>-5,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-31,68%</t>
+          <t>-9,31%</t>
         </is>
       </c>
     </row>
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 52,38</t>
+          <t>7,87; 53,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 14,63</t>
+          <t>-38,92; 17,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,72; 6,68</t>
+          <t>-30,41; 19,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 149,0</t>
+          <t>11,98; 156,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-57,54; 34,16</t>
+          <t>-55,6; 37,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-69,36; 13,02</t>
+          <t>-43,74; 44,36</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,55</t>
+          <t>-9,75</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>-17,5%</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 22,56</t>
+          <t>-25,89; 21,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 44,47</t>
+          <t>-1,38; 44,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 42,51</t>
+          <t>-30,38; 9,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,0; 48,79</t>
+          <t>-35,41; 45,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 128,38</t>
+          <t>-2,4; 121,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 106,81</t>
+          <t>-47,37; 19,47</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>1,49</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-0,24%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 13,83</t>
+          <t>-36,61; 13,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-44,35; 30,33</t>
+          <t>-43,78; 34,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,63; 24,29</t>
+          <t>-20,5; 25,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,53; 19,25</t>
+          <t>-42,27; 18,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-59,04; 86,31</t>
+          <t>-57,24; 106,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 41,9</t>
+          <t>-26,48; 43,87</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-22,02</t>
+          <t>-19,14</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-30,59%</t>
+          <t>-27,31%</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 40,21</t>
+          <t>-9,84; 39,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 18,24</t>
+          <t>-28,29; 17,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,79; 19,53</t>
+          <t>-53,93; 21,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 92,45</t>
+          <t>-10,85; 88,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 38,33</t>
+          <t>-39,98; 34,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,6; 35,64</t>
+          <t>-65,23; 43,09</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27,78</t>
+          <t>23,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 29,46</t>
+          <t>-19,31; 31,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 56,73</t>
+          <t>-21,97; 53,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 63,3</t>
+          <t>-10,52; 59,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 49,09</t>
+          <t>-21,23; 53,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 198,23</t>
+          <t>-22,91; 136,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 303,74</t>
+          <t>-15,98; 239,71</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-15,63</t>
+          <t>-15,67</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-20,56%</t>
+          <t>-21,12%</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 32,01</t>
+          <t>-35,14; 30,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 55,55</t>
+          <t>-24,29; 54,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,47; 15,52</t>
+          <t>-48,72; 17,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,27; 83,55</t>
+          <t>-52,35; 69,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,29; 478,75</t>
+          <t>-48,21; 487,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,18; 23,21</t>
+          <t>-58,94; 29,82</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>-4,83</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-3,94%</t>
+          <t>-8,67%</t>
         </is>
       </c>
     </row>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 24,3</t>
+          <t>-16,4; 26,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 23,76</t>
+          <t>-36,66; 21,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 21,27</t>
+          <t>-26,76; 18,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,86; 59,37</t>
+          <t>-25,42; 61,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-38,89; 41,01</t>
+          <t>-44,4; 35,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,57; 50,12</t>
+          <t>-40,35; 43,12</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1365,17 +1365,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 23,82</t>
+          <t>-26,54; 21,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 34,09</t>
+          <t>-10,9; 33,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 38,73</t>
+          <t>-36,35; 39,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1385,17 +1385,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,16; 56,03</t>
+          <t>-40,3; 49,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 103,54</t>
+          <t>-20,1; 107,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,02; 96,69</t>
+          <t>-51,26; 93,96</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-4,98</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-0,85%</t>
+          <t>-8,36%</t>
         </is>
       </c>
     </row>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 14,34</t>
+          <t>-4,42; 14,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 16,58</t>
+          <t>-3,41; 17,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 17,95</t>
+          <t>-15,53; 5,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 24,75</t>
+          <t>-6,48; 25,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 33,29</t>
+          <t>-5,76; 33,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 34,33</t>
+          <t>-23,62; 9,71</t>
         </is>
       </c>
     </row>
